--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129462997</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>129462085</v>
       </c>
       <c r="B9" t="n">
-        <v>92920</v>
+        <v>92923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1582,6 +1582,1297 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130016514</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora Björnfallet, Stora Björnfallet, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>470430</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6539024</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska födohack på rotvälta av tall.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130015460</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>470200</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6539357</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130015440</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>470222</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6539356</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130016720</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>470511</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6539027</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska födohack på låga av tall.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130016321</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>470367</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6539113</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska födohack på stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130016578</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>470481</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6539015</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska födohack på låga av tall.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130015641</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>470158</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6539170</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Varnar med andra mesar.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130015474</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>470196</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6539341</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På sten.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130016657</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>470478</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6539018</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack av tretåig hackspett på dubbeltall märkt med rött märkband.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130016214</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>470342</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6539171</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130016540</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stora Björnfallet, Stora Björnfallet, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>470445</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6539019</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre födohack på stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>129462085</v>
       </c>
       <c r="B9" t="n">
-        <v>92923</v>
+        <v>92924</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130015440</v>
+        <v>130016720</v>
       </c>
       <c r="B12" t="n">
         <v>57737</v>
@@ -1854,14 +1854,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sjökärret, Sjökärret, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470222</v>
+        <v>470511</v>
       </c>
       <c r="R12" t="n">
-        <v>6539356</v>
+        <v>6539027</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,7 +1935,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130016720</v>
+        <v>130015440</v>
       </c>
       <c r="B13" t="n">
         <v>57737</v>
@@ -1971,14 +1971,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470511</v>
+        <v>470222</v>
       </c>
       <c r="R13" t="n">
-        <v>6539027</v>
+        <v>6539356</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -2286,42 +2286,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130015641</v>
+        <v>130015474</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>56930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2330,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470158</v>
+        <v>470196</v>
       </c>
       <c r="R16" t="n">
-        <v>6539170</v>
+        <v>6539341</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2365,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,12 +2371,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Varnar med andra mesar.</t>
+          <t>På sten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,38 +2403,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130015474</v>
+        <v>130015641</v>
       </c>
       <c r="B17" t="n">
-        <v>56930</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470196</v>
+        <v>470158</v>
       </c>
       <c r="R17" t="n">
-        <v>6539341</v>
+        <v>6539170</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sten.</t>
+          <t>Varnar med andra mesar.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129462997</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>129462085</v>
       </c>
       <c r="B9" t="n">
-        <v>92924</v>
+        <v>92941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130015641</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130016720</v>
+        <v>130015440</v>
       </c>
       <c r="B11" t="n">
         <v>57738</v>
@@ -1738,14 +1738,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470511</v>
+        <v>470222</v>
       </c>
       <c r="R11" t="n">
-        <v>6539027</v>
+        <v>6539356</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,7 +1819,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130015440</v>
+        <v>130016720</v>
       </c>
       <c r="B12" t="n">
         <v>57738</v>
@@ -1855,14 +1855,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sjökärret, Sjökärret, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470222</v>
+        <v>470511</v>
       </c>
       <c r="R12" t="n">
-        <v>6539356</v>
+        <v>6539027</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2170,42 +2170,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130015641</v>
+        <v>130015474</v>
       </c>
       <c r="B15" t="n">
-        <v>57900</v>
+        <v>56931</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2214,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470158</v>
+        <v>470196</v>
       </c>
       <c r="R15" t="n">
-        <v>6539170</v>
+        <v>6539341</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2249,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,12 +2255,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Varnar med andra mesar.</t>
+          <t>På sten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,38 +2287,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130015474</v>
+        <v>130015641</v>
       </c>
       <c r="B16" t="n">
-        <v>56931</v>
+        <v>57900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470196</v>
+        <v>470158</v>
       </c>
       <c r="R16" t="n">
-        <v>6539341</v>
+        <v>6539170</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sten.</t>
+          <t>Varnar med andra mesar.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129462997</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>130016514</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>130015460</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130015440</v>
+        <v>130016720</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,14 +1738,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sjökärret, Sjökärret, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470222</v>
+        <v>470511</v>
       </c>
       <c r="R11" t="n">
-        <v>6539356</v>
+        <v>6539027</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130016720</v>
+        <v>130015440</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,14 +1855,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470511</v>
+        <v>470222</v>
       </c>
       <c r="R12" t="n">
-        <v>6539027</v>
+        <v>6539356</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,7 +1939,7 @@
         <v>130016321</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>130016578</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,38 +2170,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130015474</v>
+        <v>130015641</v>
       </c>
       <c r="B15" t="n">
-        <v>56931</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2210,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470196</v>
+        <v>470158</v>
       </c>
       <c r="R15" t="n">
-        <v>6539341</v>
+        <v>6539170</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2245,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,12 +2259,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På sten.</t>
+          <t>Varnar med andra mesar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,42 +2291,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130015641</v>
+        <v>130015474</v>
       </c>
       <c r="B16" t="n">
-        <v>57900</v>
+        <v>57016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470158</v>
+        <v>470196</v>
       </c>
       <c r="R16" t="n">
-        <v>6539170</v>
+        <v>6539341</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Varnar med andra mesar.</t>
+          <t>På sten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,7 +2411,7 @@
         <v>130016657</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>130016214</v>
       </c>
       <c r="B18" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>130016540</v>
       </c>
       <c r="B19" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>130113032</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>130112901</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129461517</v>
       </c>
       <c r="B3" t="n">
-        <v>56926</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129462167</v>
       </c>
       <c r="B4" t="n">
-        <v>56926</v>
+        <v>57016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129461517</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129462167</v>
       </c>
       <c r="B4" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130015474</v>
       </c>
       <c r="B16" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>130113032</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>130112901</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>130501748</v>
       </c>
       <c r="B22" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>130501776</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129461517</v>
       </c>
       <c r="B3" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129462167</v>
       </c>
       <c r="B4" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130015474</v>
       </c>
       <c r="B16" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>130501748</v>
       </c>
       <c r="B22" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>130501776</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129461517</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129462167</v>
       </c>
       <c r="B4" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130015474</v>
       </c>
       <c r="B16" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>130501748</v>
       </c>
       <c r="B22" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>130501776</v>
       </c>
       <c r="B23" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129461517</v>
       </c>
       <c r="B3" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129462167</v>
       </c>
       <c r="B4" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130015474</v>
       </c>
       <c r="B16" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>130501748</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>130501776</v>
       </c>
       <c r="B23" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -2994,7 +2994,7 @@
         <v>130501748</v>
       </c>
       <c r="B22" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>130501776</v>
       </c>
       <c r="B23" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129462997</v>
+        <v>130015440</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470576</v>
+        <v>470222</v>
       </c>
       <c r="R2" t="n">
-        <v>6539029</v>
+        <v>6539356</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -744,27 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hördes tydligt när andra mesar varnade.</t>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129461517</v>
+        <v>130015460</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470446</v>
+        <v>470200</v>
       </c>
       <c r="R3" t="n">
-        <v>6539141</v>
+        <v>6539357</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,27 +862,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Uppflog tjäder.</t>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129462167</v>
+        <v>130016214</v>
       </c>
       <c r="B4" t="n">
-        <v>57073</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,39 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470543</v>
+        <v>470342</v>
       </c>
       <c r="R4" t="n">
-        <v>6538975</v>
+        <v>6539171</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,22 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,39 +1014,39 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129461516</v>
+        <v>130016321</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470465</v>
+        <v>470367</v>
       </c>
       <c r="R5" t="n">
-        <v>6539086</v>
+        <v>6539113</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1085,22 +1096,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska födohack på stående död gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,39 +1131,39 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129462961</v>
+        <v>130016514</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1163,14 +1179,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Stora Björnfallet, Stora Björnfallet, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470571</v>
+        <v>470430</v>
       </c>
       <c r="R6" t="n">
-        <v>6538926</v>
+        <v>6539024</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,27 +1213,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska o äldre spår på samma tall</t>
+          <t>Färska födohack på rotvälta av tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,39 +1248,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129462318</v>
+        <v>130016540</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,14 +1296,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Stora Björnfallet, Stora Björnfallet, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470592</v>
+        <v>470445</v>
       </c>
       <c r="R7" t="n">
-        <v>6538947</v>
+        <v>6539019</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1314,22 +1330,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre födohack på stående död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,39 +1365,39 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129461604</v>
+        <v>130016578</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1387,19 +1408,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470480</v>
+        <v>470481</v>
       </c>
       <c r="R8" t="n">
-        <v>6539086</v>
+        <v>6539015</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1426,22 +1447,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,26 +1482,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130016514</v>
+        <v>130016720</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1504,14 +1530,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Björnfallet, Stora Björnfallet, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470430</v>
+        <v>470511</v>
       </c>
       <c r="R9" t="n">
-        <v>6539024</v>
+        <v>6539027</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1543,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,12 +1579,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska födohack på rotvälta av tall.</t>
+          <t>Färska födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,14 +1611,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130015460</v>
+        <v>130112901</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1625,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470200</v>
+        <v>470238</v>
       </c>
       <c r="R10" t="n">
-        <v>6539357</v>
+        <v>6539152</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1655,27 +1681,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>Färska födohack på stående död gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130016720</v>
+        <v>129461516</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,16 +1739,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1733,19 +1759,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470511</v>
+        <v>470465</v>
       </c>
       <c r="R11" t="n">
-        <v>6539027</v>
+        <v>6539086</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1772,27 +1798,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,22 +1828,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130015440</v>
+        <v>129461604</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,16 +1851,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1850,19 +1871,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sjökärret, Sjökärret, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470222</v>
+        <v>470480</v>
       </c>
       <c r="R12" t="n">
-        <v>6539356</v>
+        <v>6539086</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1889,27 +1910,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,22 +1940,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130016321</v>
+        <v>129462318</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,16 +1963,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1967,19 +1983,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjökärret, Sjökärret, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470367</v>
+        <v>470592</v>
       </c>
       <c r="R13" t="n">
-        <v>6539113</v>
+        <v>6538947</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2006,27 +2022,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska födohack på stående död gran.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,22 +2052,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130016578</v>
+        <v>129462961</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,16 +2075,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2093,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470481</v>
+        <v>470571</v>
       </c>
       <c r="R14" t="n">
-        <v>6539015</v>
+        <v>6538926</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2123,27 +2134,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall.</t>
+          <t>Färska o äldre spår på samma tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,22 +2169,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130015641</v>
+        <v>130016657</v>
       </c>
       <c r="B15" t="n">
-        <v>57985</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,43 +2192,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sjökärret, Sjökärret, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470158</v>
+        <v>470478</v>
       </c>
       <c r="R15" t="n">
-        <v>6539170</v>
+        <v>6539018</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2249,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,12 +2266,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Varnar med andra mesar.</t>
+          <t>Färska och äldre ringhack av tretåig hackspett på dubbeltall märkt med rött märkband.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,53 +2298,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130015474</v>
+        <v>130113032</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjökärret, Sjökärret, Vg</t>
+          <t>Vargavidderna Gryten SV, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470196</v>
+        <v>470264</v>
       </c>
       <c r="R16" t="n">
-        <v>6539341</v>
+        <v>6539218</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2361,27 +2371,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På sten.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,62 +2401,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130016657</v>
+        <v>129461402</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470478</v>
+        <v>470430</v>
       </c>
       <c r="R17" t="n">
-        <v>6539018</v>
+        <v>6539198</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2478,27 +2483,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack av tretåig hackspett på dubbeltall märkt med rött märkband.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,50 +2525,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130016214</v>
+        <v>129461517</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470342</v>
+        <v>470446</v>
       </c>
       <c r="R18" t="n">
-        <v>6539171</v>
+        <v>6539141</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2595,27 +2590,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga.</t>
+          <t>Uppflog tjäder.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,50 +2637,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130016540</v>
+        <v>129462167</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Björnfallet, Stora Björnfallet, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470445</v>
+        <v>470543</v>
       </c>
       <c r="R19" t="n">
-        <v>6539019</v>
+        <v>6538975</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2712,27 +2707,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre födohack på stående död gran.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,68 +2737,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130113032</v>
+        <v>130015474</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vargavidderna Gryten SV, Vargaviddernas naturreservat, Vg</t>
+          <t>Sjökärret, Sjökärret, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470264</v>
+        <v>470196</v>
       </c>
       <c r="R20" t="n">
-        <v>6539218</v>
+        <v>6539341</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2832,22 +2819,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På sten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,50 +2854,50 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130112901</v>
+        <v>130016003</v>
       </c>
       <c r="B21" t="n">
-        <v>57849</v>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2914,10 +2906,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470238</v>
+        <v>470316</v>
       </c>
       <c r="R21" t="n">
-        <v>6539152</v>
+        <v>6539122</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2944,27 +2936,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska födohack på stående död gran</t>
+          <t>Nedanför tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,10 +2983,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130501748</v>
+        <v>129462997</v>
       </c>
       <c r="B22" t="n">
-        <v>58037</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,26 +3012,20 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vargavidderna Gryten SV, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470232</v>
+        <v>470576</v>
       </c>
       <c r="R22" t="n">
-        <v>6539162</v>
+        <v>6539029</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3066,22 +3052,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hördes tydligt när andra mesar varnade.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,22 +3087,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130501776</v>
+        <v>129464111</v>
       </c>
       <c r="B23" t="n">
-        <v>57875</v>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3119,47 +3110,49 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vargavidderna Gryten SV, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>470232</v>
+        <v>470625</v>
       </c>
       <c r="R23" t="n">
-        <v>6539162</v>
+        <v>6538891</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3183,22 +3176,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,15 +3206,253 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130015641</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>470158</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6539170</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Varnar med andra mesar.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130501704</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vargavidderna Gryten SV, Vargaviddernas naturreservat, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>470232</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6539162</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>David Tverling</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>David Tverling</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60580-2025 artfynd.xlsx
+++ b/artfynd/A 60580-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130015440</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130015460</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130016214</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130016321</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130016514</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130016540</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1491,6 +1526,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130016578</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130016720</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,6 +1770,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130112901</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129461516</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1949,6 +2004,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129461604</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2061,6 +2121,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462318</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2178,6 +2243,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462961</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130016657</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2410,6 +2485,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130113032</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2522,6 +2602,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129461402</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2634,6 +2719,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129461517</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2746,6 +2836,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462167</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2863,6 +2958,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130015474</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2980,6 +3080,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130016003</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3096,6 +3201,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462997</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3215,6 +3325,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129464111</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3336,6 +3451,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130015641</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3453,8 +3573,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130501704</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>